--- a/dados_auxiliares/procv_orgao.xlsx
+++ b/dados_auxiliares/procv_orgao.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x526325\OneDrive - rede.sp\painel orçamentário\python\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327B0D1C-F61A-498C-BB26-B538FDC04D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>cod_orgao</t>
   </si>
@@ -46,12 +40,21 @@
   </si>
   <si>
     <t>FAASP</t>
+  </si>
+  <si>
+    <t>SGM</t>
+  </si>
+  <si>
+    <t>CGM</t>
+  </si>
+  <si>
+    <t>SMJ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -106,11 +109,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1903B466-BE54-4747-8E2A-E7C5C865588C}" name="Tabela1" displayName="Tabela1" ref="A1:B5" totalsRowShown="0">
-  <autoFilter ref="A1:B5" xr:uid="{1903B466-BE54-4747-8E2A-E7C5C865588C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:B8" totalsRowShown="0">
+  <autoFilter ref="A1:B8"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F70D6BC9-B8BE-47C3-8D03-536A7722FE79}" name="cod_orgao" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{EC43B0C3-07C9-4311-A5D4-3F74F09A7B3D}" name="orgao"/>
+    <tableColumn id="1" name="cod_orgao" dataDxfId="0"/>
+    <tableColumn id="2" name="orgao"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -371,15 +374,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -425,6 +428,30 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
